--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.74639873131574</v>
+        <v>7.108789793838807</v>
       </c>
       <c r="D2" t="n">
-        <v>43.3230081303699</v>
+        <v>7.039988821185108</v>
       </c>
       <c r="E2" t="n">
-        <v>6.43019839273761</v>
+        <v>1.044907238819862</v>
       </c>
       <c r="F2" t="n">
-        <v>10.69186534149688</v>
+        <v>1.737428117993243</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.19360079261584</v>
+        <v>7.993960128800074</v>
       </c>
       <c r="D3" t="n">
-        <v>49.555109693406</v>
+        <v>8.052705325178476</v>
       </c>
       <c r="E3" t="n">
-        <v>6.43019839273761</v>
+        <v>1.044907238819862</v>
       </c>
       <c r="F3" t="n">
-        <v>10.69186534149688</v>
+        <v>1.737428117993243</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.2688092160662</v>
+        <v>9.631181497610758</v>
       </c>
       <c r="D4" t="n">
-        <v>68.46841688583177</v>
+        <v>11.12611774394766</v>
       </c>
       <c r="E4" t="n">
-        <v>6.43019839273761</v>
+        <v>1.044907238819862</v>
       </c>
       <c r="F4" t="n">
-        <v>10.69186534149688</v>
+        <v>1.737428117993243</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
